--- a/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_clap_distilbert-base-uncased_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/DistilBERT-base-uncased/RESULT_clap_distilbert-base-uncased_zeroshot.xlsx
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2975479041713724</v>
+        <v>0.2975479041713725</v>
       </c>
     </row>
     <row r="5">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.423557946999608</v>
+        <v>15.8777239230003</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001141185982333203</v>
+        <v>0.005292574641000101</v>
       </c>
     </row>
   </sheetData>
